--- a/it_request_forms/027_employee_equipment_order_request_form--it_request_forms.xlsx
+++ b/it_request_forms/027_employee_equipment_order_request_form--it_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'laptop',_'value':_1}</t>
+          <t>laptop</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Laptop', 'value': 1}</t>
+          <t>Laptop</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'mobile_phone',_'value':_2}</t>
+          <t>mobile_phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Mobile Phone', 'value': 2}</t>
+          <t>Mobile Phone</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'tablet',_'value':_3}</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Tablet', 'value': 3}</t>
+          <t>Tablet</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'desk',_'value':_1}</t>
+          <t>desk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Desk', 'value': 1}</t>
+          <t>Desk</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'chair',_'value':_2}</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Chair', 'value': 2}</t>
+          <t>Chair</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'desk_lamp',_'value':_3}</t>
+          <t>desk_lamp</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Desk Lamp', 'value': 3}</t>
+          <t>Desk Lamp</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'marketing_campaign',_'value':_1}</t>
+          <t>marketing_campaign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Marketing Campaign', 'value': 1}</t>
+          <t>Marketing Campaign</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'sales_training',_'value':_2}</t>
+          <t>sales_training</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Sales Training', 'value': 2}</t>
+          <t>Sales Training</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'product_launch',_'value':_3}</t>
+          <t>product_launch</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Product Launch', 'value': 3}</t>
+          <t>Product Launch</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'marketing',_'value':_1}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Marketing', 'value': 1}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'sales',_'value':_2}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Sales', 'value': 2}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'finance',_'value':_3}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Finance', 'value': 3}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'jane_doe',_'value':_1}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Doe', 'value': 1}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'john_doe',_'value':_2}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'John Doe', 'value': 2}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'alice_smith',_'value':_3}</t>
+          <t>alice_smith</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Alice Smith', 'value': 3}</t>
+          <t>Alice Smith</t>
         </is>
       </c>
     </row>
